--- a/TestData/T1649_AdditionalClientsSubjectRequired.xlsx
+++ b/TestData/T1649_AdditionalClientsSubjectRequired.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C451CDD0-780C-4F8E-AFB5-519416534319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6684741-8103-4B78-9F4A-AF5411648B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -131,6 +128,9 @@
   </si>
   <si>
     <t>CB Alliance</t>
+  </si>
+  <si>
+    <t>CSDN-0000001546</t>
   </si>
 </sst>
 </file>
@@ -458,26 +458,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,52 +500,52 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P1" s="1"/>
       <c r="R1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="AG1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AH1" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="AI1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -554,52 +554,52 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI2" t="s">
         <v>32</v>
-      </c>
-      <c r="O2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -611,26 +611,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
